--- a/HBM model.xlsx
+++ b/HBM model.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sean/Desktop/Project 2/3D_Bistable_Conformal_Kirigami/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2241CC3-59F4-874F-BDF6-F3A02AA643D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BAEFA8-3F26-6B42-93EA-432921B806EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="18500" xr2:uid="{D213EE12-E565-C749-8B56-1D096127A921}"/>
+    <workbookView xWindow="34560" yWindow="500" windowWidth="38400" windowHeight="18600" activeTab="1" xr2:uid="{D213EE12-E565-C749-8B56-1D096127A921}"/>
   </bookViews>
   <sheets>
     <sheet name="HBM - Energy - N" sheetId="1" r:id="rId1"/>
+    <sheet name="Experiment material" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>N(number of segments)</t>
   </si>
@@ -44,14 +45,51 @@
     <t>Energy</t>
   </si>
   <si>
-    <t>Actual energy</t>
+    <t>Evenly distributed</t>
+  </si>
+  <si>
+    <t>Ends clustered</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Website</t>
+  </si>
+  <si>
+    <t>2.3 mm thick rubber sheets</t>
+  </si>
+  <si>
+    <t>(no smell)</t>
+  </si>
+  <si>
+    <t>https://hobarts.com/products/2-3mm-no-smell-grey-laser-rubber?variant=40677129945272</t>
+  </si>
+  <si>
+    <t>Bistable Auxetic Surface Structures</t>
+  </si>
+  <si>
+    <t>Reference paper</t>
+  </si>
+  <si>
+    <t>Durable bistable auxetics made of rigid solids</t>
+  </si>
+  <si>
+    <t>Material: Delrin® Acetal Resin
+Specimen thickness: 1.6 mm</t>
+  </si>
+  <si>
+    <t>1.6 mm Delrin® Acetal Resin sheet</t>
+  </si>
+  <si>
+    <t>https://www.par-direct.co.uk/product-details/PSHT/WEB-ACCN-2X1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -61,6 +99,28 @@
     </font>
     <font>
       <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -84,15 +144,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -123,6 +191,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2880" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Energy(evenly distributed)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -136,7 +229,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="2880" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -173,7 +266,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'HBM - Energy - N'!$A$2</c:f>
+              <c:f>'HBM - Energy - N'!$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -208,7 +301,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'HBM - Energy - N'!$B$1:$AO$1</c:f>
+              <c:f>'HBM - Energy - N'!$B$2:$AO$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="40"/>
@@ -337,7 +430,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'HBM - Energy - N'!$B$2:$AO$2</c:f>
+              <c:f>'HBM - Energy - N'!$B$3:$AO$3</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="40"/>
@@ -525,7 +618,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -587,7 +680,582 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="826896288"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="2400"/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="3360" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Energy(ends clustered)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="3360" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.4701648170721146E-2"/>
+          <c:y val="1.3458563535911603E-2"/>
+          <c:w val="0.90178404515282984"/>
+          <c:h val="0.86694305477008748"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'HBM - Energy - N'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Energy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'HBM - Energy - N'!$B$8:$AO$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="40"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'HBM - Energy - N'!$B$9:$AO$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="40"/>
+                <c:pt idx="0">
+                  <c:v>66436.866978279795</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50219.964768100101</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>49287.702337093098</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>48928.5043811703</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48748.239501733602</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>48640.380485631402</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>48527.543542268497</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>48456.398099748301</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>48437.927515590098</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>48419.195268704701</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>48377.482856916402</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>48343.626526206899</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>48314.255492107703</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>48289.562599116303</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>48269.502577753701</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>48261.7375267756</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>48239.810024788399</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>48225.811324217502</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>48198.233570921802</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>48202.040991779402</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>48175.334444532098</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>48188.540322467903</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>48136.894490625396</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>48137.263556381797</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>48146.468147359999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>48139.483431222798</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>48132.949172388697</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>48126.9200282815</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>48121.528209496697</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>48147.079894299</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>48141.806221946303</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>48093.169829868602</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>48088.075740118198</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>48084.126203518703</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>48080.375215364598</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>48076.848259287501</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>48073.489301079302</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>48070.3204773814</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>48067.295069826097</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>48064.432415349103</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-698B-344A-9B28-E24A87331B09}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="826896288"/>
+        <c:axId val="1517072592"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="826896288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1517072592"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1517072592"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -645,7 +1313,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="2800"/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -698,6 +1366,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1214,20 +1922,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1974850</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>69851</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>141873</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1247,6 +2471,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>819150</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>122822</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECC56412-F9E0-D045-A3FB-545BFE3B4E33}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1572,276 +2834,634 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C13FE04-D6ED-B54B-8140-50EF384860B6}">
-  <dimension ref="A1:AO4"/>
+  <dimension ref="A1:AO13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.1640625" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="41" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="41" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="1" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:41" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B2" s="3">
         <v>5</v>
       </c>
-      <c r="C1" s="1">
+      <c r="C2" s="3">
         <v>10</v>
       </c>
-      <c r="D1" s="1">
+      <c r="D2" s="3">
         <v>15</v>
       </c>
-      <c r="E1" s="1">
+      <c r="E2" s="3">
         <v>20</v>
       </c>
-      <c r="F1" s="1">
+      <c r="F2" s="3">
         <v>25</v>
       </c>
-      <c r="G1" s="1">
+      <c r="G2" s="3">
         <v>30</v>
       </c>
-      <c r="H1" s="1">
+      <c r="H2" s="3">
         <v>35</v>
       </c>
-      <c r="I1" s="1">
+      <c r="I2" s="3">
         <v>40</v>
       </c>
-      <c r="J1" s="1">
+      <c r="J2" s="3">
         <v>45</v>
       </c>
-      <c r="K1" s="1">
+      <c r="K2" s="3">
         <v>50</v>
       </c>
-      <c r="L1" s="1">
+      <c r="L2" s="3">
         <v>55</v>
       </c>
-      <c r="M1" s="1">
+      <c r="M2" s="3">
         <v>60</v>
       </c>
-      <c r="N1" s="1">
+      <c r="N2" s="3">
         <v>65</v>
       </c>
-      <c r="O1" s="1">
+      <c r="O2" s="3">
         <v>70</v>
       </c>
-      <c r="P1" s="1">
+      <c r="P2" s="3">
         <v>75</v>
       </c>
-      <c r="Q1" s="1">
+      <c r="Q2" s="3">
         <v>80</v>
       </c>
-      <c r="R1" s="1">
+      <c r="R2" s="3">
         <v>85</v>
       </c>
-      <c r="S1" s="1">
+      <c r="S2" s="3">
         <v>90</v>
       </c>
-      <c r="T1" s="1">
+      <c r="T2" s="3">
         <v>95</v>
       </c>
-      <c r="U1" s="1">
+      <c r="U2" s="3">
         <v>100</v>
       </c>
-      <c r="V1" s="1">
+      <c r="V2" s="3">
         <v>105</v>
       </c>
-      <c r="W1" s="1">
+      <c r="W2" s="3">
         <v>110</v>
       </c>
-      <c r="X1" s="1">
+      <c r="X2" s="3">
         <v>115</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="Y2" s="3">
         <v>120</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Z2" s="3">
         <v>125</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="AA2" s="3">
         <v>130</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="AB2" s="3">
         <v>135</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="AC2" s="3">
         <v>140</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="AD2" s="3">
         <v>145</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="AE2" s="3">
         <v>150</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="AF2" s="3">
         <v>155</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="AG2" s="3">
         <v>160</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="AH2" s="3">
         <v>165</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="AI2" s="3">
         <v>170</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AJ2" s="3">
         <v>175</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AK2" s="3">
         <v>180</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AL2" s="3">
         <v>185</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AM2" s="3">
         <v>190</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AN2" s="3">
         <v>195</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AO2" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:41" s="1" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:41" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B3" s="4">
         <v>199991.84869982401</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C3" s="4">
         <v>169152.7146494</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D3" s="4">
         <v>106265.94116608601</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E3" s="4">
         <v>89928.0569303058</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F3" s="4">
         <v>79737.441118766001</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G3" s="4">
         <v>73208.924320845195</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H3" s="4">
         <v>68872.460959136006</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I3" s="4">
         <v>65657.584069569901</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J3" s="4">
         <v>63340.041373954497</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K3" s="4">
         <v>61535.812862959101</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L3" s="4">
         <v>60192.083021083701</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M3" s="4">
         <v>59039.677774107702</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N3" s="4">
         <v>58049.620339410998</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O3" s="4">
         <v>57199.443733052103</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P3" s="4">
         <v>56517.072518246503</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q3" s="4">
         <v>55933.4182576245</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R3" s="4">
         <v>55418.346602750098</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S3" s="4">
         <v>54961.849512411303</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T3" s="4">
         <v>54558.133069928699</v>
       </c>
-      <c r="U2" s="2">
+      <c r="U3" s="4">
         <v>54222.392990118802</v>
       </c>
-      <c r="V2" s="2">
+      <c r="V3" s="4">
         <v>53880.776782510897</v>
       </c>
-      <c r="W2" s="2">
+      <c r="W3" s="4">
         <v>53591.957908481701</v>
       </c>
-      <c r="X2" s="2">
+      <c r="X3" s="4">
         <v>53341.708252222197</v>
       </c>
-      <c r="Y2" s="2">
+      <c r="Y3" s="4">
         <v>53106.732554729198</v>
       </c>
-      <c r="Z2" s="2">
+      <c r="Z3" s="4">
         <v>52870.953892797799</v>
       </c>
-      <c r="AA2" s="2">
+      <c r="AA3" s="4">
         <v>52665.0882573524</v>
       </c>
-      <c r="AB2" s="2">
+      <c r="AB3" s="4">
         <v>52480.427632254097</v>
       </c>
-      <c r="AC2" s="2">
+      <c r="AC3" s="4">
         <v>52305.490362175202</v>
       </c>
-      <c r="AD2" s="2">
+      <c r="AD3" s="4">
         <v>52156.634913088899</v>
       </c>
-      <c r="AE2" s="2">
+      <c r="AE3" s="4">
         <v>52003.2656426787</v>
       </c>
-      <c r="AF2" s="2">
+      <c r="AF3" s="4">
         <v>51865.090556925097</v>
       </c>
-      <c r="AG2" s="2">
+      <c r="AG3" s="4">
         <v>51735.1179086958</v>
       </c>
-      <c r="AH2" s="2">
+      <c r="AH3" s="4">
         <v>51622.598470359997</v>
       </c>
-      <c r="AI2" s="2">
+      <c r="AI3" s="4">
         <v>51498.947169052801</v>
       </c>
-      <c r="AJ2" s="2">
+      <c r="AJ3" s="4">
         <v>51397.297293396099</v>
       </c>
-      <c r="AK2" s="2">
+      <c r="AK3" s="4">
         <v>51293.635754876603</v>
       </c>
-      <c r="AL2" s="2">
+      <c r="AL3" s="4">
         <v>51199.780602900399</v>
       </c>
-      <c r="AM2" s="2">
+      <c r="AM3" s="4">
         <v>51113.9059441344</v>
       </c>
-      <c r="AN2" s="2">
+      <c r="AN3" s="4">
         <v>51028.1342106476</v>
       </c>
-      <c r="AO2" s="2">
+      <c r="AO3" s="4">
         <v>50944.6290345503</v>
       </c>
     </row>
-    <row r="3" spans="1:41" s="1" customFormat="1" ht="22" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:41" s="1" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1">
-        <v>44420</v>
-      </c>
+    <row r="4" spans="1:41" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:41" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:41" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:41" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3">
+        <v>15</v>
+      </c>
+      <c r="E8" s="3">
+        <v>20</v>
+      </c>
+      <c r="F8" s="3">
+        <v>25</v>
+      </c>
+      <c r="G8" s="3">
+        <v>30</v>
+      </c>
+      <c r="H8" s="3">
+        <v>35</v>
+      </c>
+      <c r="I8" s="3">
+        <v>40</v>
+      </c>
+      <c r="J8" s="3">
+        <v>45</v>
+      </c>
+      <c r="K8" s="3">
+        <v>50</v>
+      </c>
+      <c r="L8" s="3">
+        <v>55</v>
+      </c>
+      <c r="M8" s="3">
+        <v>60</v>
+      </c>
+      <c r="N8" s="3">
+        <v>65</v>
+      </c>
+      <c r="O8" s="3">
+        <v>70</v>
+      </c>
+      <c r="P8" s="3">
+        <v>75</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>80</v>
+      </c>
+      <c r="R8" s="3">
+        <v>85</v>
+      </c>
+      <c r="S8" s="3">
+        <v>90</v>
+      </c>
+      <c r="T8" s="3">
+        <v>95</v>
+      </c>
+      <c r="U8" s="3">
+        <v>100</v>
+      </c>
+      <c r="V8" s="3">
+        <v>105</v>
+      </c>
+      <c r="W8" s="3">
+        <v>110</v>
+      </c>
+      <c r="X8" s="3">
+        <v>115</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>120</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>125</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>130</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>135</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>140</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>145</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>150</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>155</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>160</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>165</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>170</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>175</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>180</v>
+      </c>
+      <c r="AL8" s="3">
+        <v>185</v>
+      </c>
+      <c r="AM8" s="3">
+        <v>190</v>
+      </c>
+      <c r="AN8" s="3">
+        <v>195</v>
+      </c>
+      <c r="AO8" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4">
+        <v>66436.866978279795</v>
+      </c>
+      <c r="C9" s="4">
+        <v>50219.964768100101</v>
+      </c>
+      <c r="D9" s="4">
+        <v>49287.702337093098</v>
+      </c>
+      <c r="E9" s="4">
+        <v>48928.5043811703</v>
+      </c>
+      <c r="F9" s="4">
+        <v>48748.239501733602</v>
+      </c>
+      <c r="G9" s="4">
+        <v>48640.380485631402</v>
+      </c>
+      <c r="H9" s="4">
+        <v>48527.543542268497</v>
+      </c>
+      <c r="I9" s="4">
+        <v>48456.398099748301</v>
+      </c>
+      <c r="J9" s="4">
+        <v>48437.927515590098</v>
+      </c>
+      <c r="K9" s="4">
+        <v>48419.195268704701</v>
+      </c>
+      <c r="L9" s="4">
+        <v>48377.482856916402</v>
+      </c>
+      <c r="M9" s="4">
+        <v>48343.626526206899</v>
+      </c>
+      <c r="N9" s="4">
+        <v>48314.255492107703</v>
+      </c>
+      <c r="O9" s="4">
+        <v>48289.562599116303</v>
+      </c>
+      <c r="P9" s="4">
+        <v>48269.502577753701</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>48261.7375267756</v>
+      </c>
+      <c r="R9" s="4">
+        <v>48239.810024788399</v>
+      </c>
+      <c r="S9" s="4">
+        <v>48225.811324217502</v>
+      </c>
+      <c r="T9" s="4">
+        <v>48198.233570921802</v>
+      </c>
+      <c r="U9" s="4">
+        <v>48202.040991779402</v>
+      </c>
+      <c r="V9" s="4">
+        <v>48175.334444532098</v>
+      </c>
+      <c r="W9" s="4">
+        <v>48188.540322467903</v>
+      </c>
+      <c r="X9" s="4">
+        <v>48136.894490625396</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>48137.263556381797</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>48146.468147359999</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>48139.483431222798</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>48132.949172388697</v>
+      </c>
+      <c r="AC9" s="4">
+        <v>48126.9200282815</v>
+      </c>
+      <c r="AD9" s="4">
+        <v>48121.528209496697</v>
+      </c>
+      <c r="AE9" s="4">
+        <v>48147.079894299</v>
+      </c>
+      <c r="AF9" s="4">
+        <v>48141.806221946303</v>
+      </c>
+      <c r="AG9" s="4">
+        <v>48093.169829868602</v>
+      </c>
+      <c r="AH9" s="4">
+        <v>48088.075740118198</v>
+      </c>
+      <c r="AI9" s="4">
+        <v>48084.126203518703</v>
+      </c>
+      <c r="AJ9" s="4">
+        <v>48080.375215364598</v>
+      </c>
+      <c r="AK9" s="4">
+        <v>48076.848259287501</v>
+      </c>
+      <c r="AL9" s="4">
+        <v>48073.489301079302</v>
+      </c>
+      <c r="AM9" s="4">
+        <v>48070.3204773814</v>
+      </c>
+      <c r="AN9" s="4">
+        <v>48067.295069826097</v>
+      </c>
+      <c r="AO9" s="4">
+        <v>48064.432415349103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" ht="22" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{824CDE78-61D0-6B44-B813-05BEFA8BDC0B}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="62.5" customWidth="1"/>
+    <col min="2" max="2" width="57" customWidth="1"/>
+    <col min="3" max="3" width="88.5" customWidth="1"/>
+    <col min="4" max="4" width="69.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="3" customFormat="1" ht="84" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:4" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:4" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:4" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:4" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:4" ht="32" x14ac:dyDescent="0.4">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" ht="32" x14ac:dyDescent="0.4">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" ht="32" x14ac:dyDescent="0.4">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" ht="32" x14ac:dyDescent="0.4">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" ht="32" x14ac:dyDescent="0.4">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" ht="32" x14ac:dyDescent="0.4">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" ht="32" x14ac:dyDescent="0.4">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" ht="32" x14ac:dyDescent="0.4">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" spans="1:2" ht="32" x14ac:dyDescent="0.4">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{A0A54BEA-DDBB-2A46-9731-CBC313FEAFE7}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{FCBBC324-0C2A-714E-8118-78845B3F5370}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>